--- a/data/trans_camb/P16A_n_R3-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P16A_n_R3-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 1,51</t>
+          <t>-0,62; 1,55</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,55</t>
+          <t>0,04; 2,65</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,64; 7,26</t>
+          <t>3,52; 6,96</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,17; 5,72</t>
+          <t>2,05; 5,42</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,56; 6,27</t>
+          <t>2,42; 6,03</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,75; 10,88</t>
+          <t>6,51; 10,6</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,02; 3,21</t>
+          <t>1,13; 3,21</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,56; 3,88</t>
+          <t>1,57; 3,8</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,83; 8,42</t>
+          <t>5,77; 8,36</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-51,09; 298,85</t>
+          <t>-54,47; 352,78</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-8,62; 541,07</t>
+          <t>-14,02; 519,27</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>221,99; 1653,7</t>
+          <t>194,57; 1430,57</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>133,38; 1449,66</t>
+          <t>85,36; 1260,14</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>146,52; 1717,38</t>
+          <t>137,86; 1455,55</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>405,33; 3210,97</t>
+          <t>413,67; 2926,84</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>73,84; 563,67</t>
+          <t>77,68; 600,2</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>98,16; 649,16</t>
+          <t>111,07; 661,13</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>404,67; 1507,98</t>
+          <t>404,53; 1453,62</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 0,85</t>
+          <t>-1,42; 0,86</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 1,27</t>
+          <t>-1,14; 1,13</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 3,53</t>
+          <t>-0,4; 3,46</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,24; 4,61</t>
+          <t>1,31; 4,84</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 2,74</t>
+          <t>-0,34; 2,68</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,42; 9,02</t>
+          <t>5,39; 8,84</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,34</t>
+          <t>0,31; 2,34</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 1,51</t>
+          <t>-0,26; 1,62</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,14; 5,59</t>
+          <t>1,87; 5,41</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-69,05; 108,09</t>
+          <t>-67,59; 116,73</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-51,92; 161,51</t>
+          <t>-52,82; 123,46</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 358,63</t>
+          <t>-8,44; 332,86</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>36,41; 300,42</t>
+          <t>33,47; 297,7</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-13,82; 181,31</t>
+          <t>-15,51; 169,76</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>170,4; 594,29</t>
+          <t>166,34; 576,93</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,45; 168,72</t>
+          <t>8,65; 160,88</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-17,52; 99,18</t>
+          <t>-12,73; 116,83</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>101,09; 393,92</t>
+          <t>86,37; 362,62</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 2,77</t>
+          <t>-0,59; 2,76</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 1,85</t>
+          <t>-0,92; 1,81</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,82; 4,09</t>
+          <t>0,93; 3,96</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 1,36</t>
+          <t>-2,51; 1,5</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 1,73</t>
+          <t>-2,45; 1,75</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 3,62</t>
+          <t>-2,48; 3,89</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 1,56</t>
+          <t>-1,06; 1,47</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 1,38</t>
+          <t>-1,1; 1,42</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,05; 3,4</t>
+          <t>0,05; 3,39</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-30,38; 368,27</t>
+          <t>-34,97; 347,17</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-46,85; 238,75</t>
+          <t>-49,02; 202,46</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>24,26; 485,08</t>
+          <t>34,27; 543,95</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-49,79; 43,68</t>
+          <t>-48,39; 53,3</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-43,65; 55,98</t>
+          <t>-44,72; 54,34</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-39,89; 104,07</t>
+          <t>-42,2; 108,69</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-32,51; 70,66</t>
+          <t>-31,96; 67,46</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-31,04; 65,02</t>
+          <t>-32,3; 64,2</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5,17; 154,27</t>
+          <t>2,46; 155,59</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 1,96</t>
+          <t>-0,87; 1,9</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 0,4</t>
+          <t>-1,74; 0,32</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,0; 4,98</t>
+          <t>1,88; 5,05</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,19; 4,9</t>
+          <t>1,25; 5,02</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,39; 3,96</t>
+          <t>0,45; 4,1</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,46; 10,08</t>
+          <t>5,35; 10,17</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,71; 2,96</t>
+          <t>0,56; 2,95</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 1,86</t>
+          <t>-0,31; 1,84</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4,61; 7,31</t>
+          <t>4,41; 7,21</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-32,22; 140,38</t>
+          <t>-34,78; 131,5</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-71,65; 33,95</t>
+          <t>-71,14; 30,91</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>68,07; 336,21</t>
+          <t>74,28; 366,1</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>28,34; 215,4</t>
+          <t>30,1; 214,25</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>8,08; 177,62</t>
+          <t>9,38; 181,46</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>141,63; 446,74</t>
+          <t>137,72; 455,55</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,82; 144,23</t>
+          <t>19,24; 149,62</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-12,54; 92,26</t>
+          <t>-11,24; 92,7</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>149,96; 349,72</t>
+          <t>151,6; 360,8</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 0,96</t>
+          <t>-0,36; 0,97</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 0,77</t>
+          <t>-0,42; 0,8</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,06; 3,93</t>
+          <t>1,93; 3,81</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,52; 3,36</t>
+          <t>1,43; 3,33</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,86; 2,58</t>
+          <t>0,86; 2,67</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,53; 7,41</t>
+          <t>4,43; 7,4</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,8; 1,95</t>
+          <t>0,82; 1,98</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,41; 1,53</t>
+          <t>0,45; 1,57</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3,79; 5,53</t>
+          <t>3,83; 5,48</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-18,65; 79,86</t>
+          <t>-22,12; 80,19</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-24,28; 64,82</t>
+          <t>-23,26; 67,84</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>116,41; 317,29</t>
+          <t>114,76; 338,13</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>52,76; 155,56</t>
+          <t>48,5; 153,73</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>28,95; 119,1</t>
+          <t>28,45; 119,01</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>166,55; 345,22</t>
+          <t>159,65; 341,34</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>35,32; 109,53</t>
+          <t>34,84; 110,5</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>18,25; 87,22</t>
+          <t>17,68; 88,81</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>170,7; 309,75</t>
+          <t>171,64; 301,54</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P16A_n_R3-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P16A_n_R3-Habitat-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5,12</t>
+          <t>5,04</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,87</t>
+          <t>9,4</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>7,12</t>
+          <t>7,28</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 1,55</t>
+          <t>-0,74; 1,61</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,04; 2,65</t>
+          <t>0,12; 2,6</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,52; 6,96</t>
+          <t>3,42; 6,95</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,05; 5,42</t>
+          <t>2,12; 5,64</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,42; 6,03</t>
+          <t>2,42; 6,1</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,51; 10,6</t>
+          <t>7,74; 11,27</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,13; 3,21</t>
+          <t>1,19; 3,19</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,57; 3,8</t>
+          <t>1,64; 3,89</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,77; 8,36</t>
+          <t>6,17; 8,56</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>534,34%</t>
+          <t>526,23%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1041,08%</t>
+          <t>1102,53%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>786,02%</t>
+          <t>804,5%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-54,47; 352,78</t>
+          <t>-55,19; 322,12</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-14,02; 519,27</t>
+          <t>-10,2; 465,58</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>194,57; 1430,57</t>
+          <t>204,55; 1422,62</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>85,36; 1260,14</t>
+          <t>110,74; 1204,93</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>137,86; 1455,55</t>
+          <t>158,62; 1450,36</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>413,67; 2926,84</t>
+          <t>453,81; 3400,98</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>77,68; 600,2</t>
+          <t>80,53; 545,59</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>111,07; 661,13</t>
+          <t>103,01; 631,84</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>404,53; 1453,62</t>
+          <t>419,73; 1534,16</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1,98</t>
+          <t>2,68</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,12</t>
+          <t>6,9</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>4,23</t>
+          <t>4,82</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 0,86</t>
+          <t>-1,39; 0,86</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 1,13</t>
+          <t>-1,1; 1,11</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 3,46</t>
+          <t>1,36; 4,03</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,31; 4,84</t>
+          <t>1,25; 4,58</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 2,68</t>
+          <t>-0,32; 2,86</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,39; 8,84</t>
+          <t>5,23; 8,63</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,31; 2,34</t>
+          <t>0,31; 2,44</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 1,62</t>
+          <t>-0,46; 1,59</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,87; 5,41</t>
+          <t>3,68; 5,9</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>130,69%</t>
+          <t>177,06%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>318,18%</t>
+          <t>308,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>225,23%</t>
+          <t>256,59%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-67,59; 116,73</t>
+          <t>-67,23; 113,11</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-52,82; 123,46</t>
+          <t>-54,86; 122,22</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-8,44; 332,86</t>
+          <t>47,45; 427,16</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>33,47; 297,7</t>
+          <t>42,77; 306,36</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-15,51; 169,76</t>
+          <t>-11,47; 171,42</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>166,34; 576,93</t>
+          <t>164,61; 576,56</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,65; 160,88</t>
+          <t>12,01; 170,17</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-12,73; 116,83</t>
+          <t>-20,6; 116,29</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>86,37; 362,62</t>
+          <t>143,77; 435,72</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2,41</t>
+          <t>2,35</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,32</t>
+          <t>2,94</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1,98</t>
+          <t>2,65</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 2,76</t>
+          <t>-0,56; 2,58</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 1,81</t>
+          <t>-0,91; 1,73</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,93; 3,96</t>
+          <t>0,81; 3,99</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 1,5</t>
+          <t>-2,59; 1,52</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 1,75</t>
+          <t>-2,35; 1,88</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 3,89</t>
+          <t>0,78; 5,01</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 1,47</t>
+          <t>-0,96; 1,51</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 1,42</t>
+          <t>-1,11; 1,37</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,05; 3,39</t>
+          <t>1,4; 3,92</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>174,65%</t>
+          <t>170,19%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>70,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>71,11%</t>
+          <t>95,4%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-34,97; 347,17</t>
+          <t>-35,21; 322,17</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-49,02; 202,46</t>
+          <t>-52,47; 210,45</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>34,27; 543,95</t>
+          <t>28,29; 537,78</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-48,39; 53,3</t>
+          <t>-50,93; 51,38</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-44,72; 54,34</t>
+          <t>-45,17; 59,33</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-42,2; 108,69</t>
+          <t>13,69; 167,01</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-31,96; 67,46</t>
+          <t>-29,24; 67,72</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-32,3; 64,2</t>
+          <t>-33,85; 64,19</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2,46; 155,59</t>
+          <t>39,47; 181,9</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3,45</t>
+          <t>3,36</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,84</t>
+          <t>8,25</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>5,84</t>
+          <t>5,96</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 1,9</t>
+          <t>-0,75; 1,86</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 0,32</t>
+          <t>-1,75; 0,27</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,88; 5,05</t>
+          <t>2,0; 4,8</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,25; 5,02</t>
+          <t>1,27; 4,73</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,45; 4,1</t>
+          <t>0,45; 3,96</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,35; 10,17</t>
+          <t>6,44; 10,03</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,56; 2,95</t>
+          <t>0,61; 2,96</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 1,84</t>
+          <t>-0,25; 1,86</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4,41; 7,21</t>
+          <t>4,75; 7,21</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>182,33%</t>
+          <t>177,55%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>263,16%</t>
+          <t>277,14%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>237,45%</t>
+          <t>242,26%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-34,78; 131,5</t>
+          <t>-37,97; 136,76</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-71,14; 30,91</t>
+          <t>-70,83; 35,4</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>74,28; 366,1</t>
+          <t>78,51; 358,54</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>30,1; 214,25</t>
+          <t>30,72; 207,03</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>9,38; 181,46</t>
+          <t>6,38; 162,65</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>137,72; 455,55</t>
+          <t>162,8; 434,8</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,24; 149,62</t>
+          <t>17,55; 142,22</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-11,24; 92,7</t>
+          <t>-9,02; 90,73</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>151,6; 360,8</t>
+          <t>156,16; 380,79</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3,05</t>
+          <t>3,26</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>6,31</t>
+          <t>6,97</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>4,75</t>
+          <t>5,17</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 0,97</t>
+          <t>-0,3; 1,03</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 0,8</t>
+          <t>-0,46; 0,74</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,93; 3,81</t>
+          <t>2,53; 4,03</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,43; 3,33</t>
+          <t>1,42; 3,36</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,86; 2,67</t>
+          <t>0,85; 2,63</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,43; 7,4</t>
+          <t>6,14; 7,96</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,82; 1,98</t>
+          <t>0,81; 1,98</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,45; 1,57</t>
+          <t>0,48; 1,51</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3,83; 5,48</t>
+          <t>4,58; 5,79</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>206,2%</t>
+          <t>220,72%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>245,29%</t>
+          <t>270,89%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>233,43%</t>
+          <t>254,44%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-22,12; 80,19</t>
+          <t>-18,88; 83,42</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-23,26; 67,84</t>
+          <t>-25,56; 61,66</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>114,76; 338,13</t>
+          <t>132,18; 336,07</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>48,5; 153,73</t>
+          <t>47,55; 151,93</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>28,45; 119,01</t>
+          <t>27,81; 120,08</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>159,65; 341,34</t>
+          <t>196,02; 362,5</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>34,84; 110,5</t>
+          <t>35,65; 110,03</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>17,68; 88,81</t>
+          <t>20,41; 83,26</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>171,64; 301,54</t>
+          <t>197,55; 333,65</t>
         </is>
       </c>
     </row>
